--- a/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T18:49:12+00:00</t>
+    <t>2024-06-11T05:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-carerelation-metadata-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:22:30+00:00</t>
+    <t>2024-06-11T05:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
